--- a/erp-server/erp-server-file/src/main/resources/excel/wms/qcStandard.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/qcStandard.xlsx
@@ -1,46 +1,33 @@
 
-<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
-<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <Application>WPS 表格</Application>
-  <HeadingPairs>
-    <vt:vector size="2" baseType="variant">
-      <vt:variant>
-        <vt:lpstr>工作表</vt:lpstr>
-      </vt:variant>
-      <vt:variant>
-        <vt:i4>1</vt:i4>
-      </vt:variant>
-    </vt:vector>
-  </HeadingPairs>
-  <TitlesOfParts>
-    <vt:vector size="1" baseType="lpstr">
-      <vt:lpstr>Sheet1</vt:lpstr>
-    </vt:vector>
-  </TitlesOfParts>
-</Properties>
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
+  <bookViews>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+  </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
+</workbook>
 </file>
 
-<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
-<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <cp:lastModifiedBy>Administrator</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2023-05-17T03:04:00Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2024-02-22T09:44:37Z</dcterms:modified>
-</cp:coreProperties>
-</file>
-
-<file path=docProps\custom.xml><?xml version="1.0" encoding="utf-8"?>
-<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="2" name="ICV">
-    <vt:lpwstr>9A75B18CBD224B648394C7EF1175288E_12</vt:lpwstr>
-  </property>
-  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="3" name="KSOProductBuildVer">
-    <vt:lpwstr>2052-12.1.0.16250</vt:lpwstr>
-  </property>
-</Properties>
-</file>
-
-<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>SKU编码</t>
   </si>
@@ -51,7 +38,13 @@
     <t>备注</t>
   </si>
   <si>
-    <t>是否禁用</t>
+    <t>状态</t>
+  </si>
+  <si>
+    <t>质检要求</t>
+  </si>
+  <si>
+    <t>质检项目</t>
   </si>
   <si>
     <t>创建人</t>
@@ -75,7 +68,13 @@
     <t>{.remark}</t>
   </si>
   <si>
-    <t>{.disabled}</t>
+    <t>{.disabledName}</t>
+  </si>
+  <si>
+    <t>{.inspectItemName}</t>
+  </si>
+  <si>
+    <t>{.inspectRequirement}</t>
   </si>
   <si>
     <t>{.createUserName}</t>
@@ -92,7 +91,7 @@
 </sst>
 </file>
 
-<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
@@ -100,16 +99,9 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
+  <fonts count="20">
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -454,27 +446,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -595,144 +572,138 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -796,7 +767,7 @@
 </styleSheet>
 </file>
 
-<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -1080,37 +1051,18 @@
 </a:theme>
 </file>
 
-<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
-  <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-  </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
-</workbook>
-</file>
-
-<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <cols>
+    <col min="2" max="3" width="14.5" customWidth="1"/>
+    <col min="4" max="8" width="24.75" customWidth="1"/>
+    <col min="9" max="9" width="15.5" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1135,33 +1087,47 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/erp-server/erp-server-file/src/main/resources/excel/wms/qcStandard.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/qcStandard.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>SKU编码</t>
   </si>
@@ -47,6 +47,12 @@
     <t>质检项目</t>
   </si>
   <si>
+    <t>产品实物</t>
+  </si>
+  <si>
+    <t>包装配件</t>
+  </si>
+  <si>
     <t>创建人</t>
   </si>
   <si>
@@ -75,6 +81,12 @@
   </si>
   <si>
     <t>{.inspectRequirement}</t>
+  </si>
+  <si>
+    <t>{.productPhysicalUrl}</t>
+  </si>
+  <si>
+    <t>{.packagingAccessoriesUrl}</t>
   </si>
   <si>
     <t>{.createUserName}</t>
@@ -1054,15 +1066,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="2" max="3" width="14.5" customWidth="1"/>
-    <col min="4" max="8" width="24.75" customWidth="1"/>
-    <col min="9" max="9" width="15.5" customWidth="1"/>
+    <col min="4" max="10" width="24.75" customWidth="1"/>
+    <col min="11" max="11" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1093,37 +1105,49 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J2" t="s">
-        <v>19</v>
+        <v>21</v>
+      </c>
+      <c r="K2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
